--- a/LISTAS_ORDENADAS/MA/Tornillos Pitones Arandelas Tuercas/PARKER.xlsx
+++ b/LISTAS_ORDENADAS/MA/Tornillos Pitones Arandelas Tuercas/PARKER.xlsx
@@ -819,14 +819,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45201.68858743707</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="20">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -848,8 +844,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11" ht="41.25" customHeight="1" s="20">
       <c r="A11" s="21" t="inlineStr">
         <is>
@@ -860,14 +854,6 @@
     <row r="12" ht="41.25" customHeight="1" s="20">
       <c r="A12" s="22" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
     <row r="21" ht="22.5" customHeight="1" s="20">
       <c r="A21" s="24" t="inlineStr">
         <is>
@@ -1250,7 +1236,6 @@
         <v>3082.117</v>
       </c>
     </row>
-    <row r="48"/>
     <row r="49" ht="23.25" customHeight="1" s="20">
       <c r="A49" s="24" t="inlineStr">
         <is>
@@ -1258,7 +1243,6 @@
         </is>
       </c>
     </row>
-    <row r="50"/>
     <row r="51" ht="18" customHeight="1" s="20">
       <c r="A51" s="9" t="inlineStr">
         <is>
@@ -1469,7 +1453,6 @@
         <v>3651.367</v>
       </c>
     </row>
-    <row r="64"/>
     <row r="65" ht="23.25" customHeight="1" s="20">
       <c r="A65" s="24" t="inlineStr">
         <is>
@@ -1477,7 +1460,6 @@
         </is>
       </c>
     </row>
-    <row r="66"/>
     <row r="67" ht="18" customHeight="1" s="20">
       <c r="A67" s="9" t="inlineStr">
         <is>
@@ -1704,7 +1686,6 @@
         <v>4043.966</v>
       </c>
     </row>
-    <row r="81"/>
     <row r="82" ht="23.25" customHeight="1" s="20">
       <c r="A82" s="24" t="inlineStr">
         <is>
@@ -1712,7 +1693,6 @@
         </is>
       </c>
     </row>
-    <row r="83"/>
     <row r="84" ht="18" customHeight="1" s="20">
       <c r="A84" s="9" t="inlineStr">
         <is>
@@ -1923,7 +1903,6 @@
         <v>7550.794</v>
       </c>
     </row>
-    <row r="97"/>
     <row r="98" ht="23.25" customHeight="1" s="20">
       <c r="A98" s="24" t="inlineStr">
         <is>
@@ -1931,7 +1910,6 @@
         </is>
       </c>
     </row>
-    <row r="99"/>
     <row r="100" ht="18" customHeight="1" s="20">
       <c r="A100" s="9" t="inlineStr">
         <is>
@@ -2110,7 +2088,6 @@
         <v>7777.371</v>
       </c>
     </row>
-    <row r="111"/>
     <row r="112" ht="23.25" customHeight="1" s="20">
       <c r="A112" s="24" t="inlineStr">
         <is>
@@ -2118,7 +2095,6 @@
         </is>
       </c>
     </row>
-    <row r="113"/>
     <row r="114" ht="18" customHeight="1" s="20">
       <c r="A114" s="9" t="inlineStr">
         <is>
@@ -2297,8 +2273,6 @@
         <v>10419.458</v>
       </c>
     </row>
-    <row r="125"/>
-    <row r="126"/>
     <row r="127" ht="20.25" customHeight="1" s="20">
       <c r="A127" s="14" t="inlineStr">
         <is>
@@ -2324,102 +2298,102 @@
     </row>
   </sheetData>
   <mergeCells count="96">
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="A128:B128"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B119:C119"/>
     <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B84:C84"/>
     <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="A128:B128"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="A82:C82"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B72:C72"/>
     <mergeCell ref="B121:C121"/>
     <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A112:C112"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="A98:C98"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B114:C114"/>
     <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="A112:C112"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B110:C110"/>
-    <mergeCell ref="A98:C98"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="A82:C82"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
     <mergeCell ref="A65:C65"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A7:D7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>
